--- a/Codelist Excel Files and Conversion Templates to XML/samplingFeatureTypes.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/samplingFeatureTypes.xlsx
@@ -1432,17 +1432,17 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>rigid_inclusion</t>
+          <t>ri_column</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>Rigid inclusion</t>
+          <t>RI column</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>A single rigid inclusion element (CMC) - the location and properties of one column in a rigid inclusion ground improvement program.</t>
+          <t>A single rigid inclusion column (CMC) - the location and properties of one column in a rigid inclusion ground improvement program.</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>ri_foundation_system</t>
+          <t>rigid_inclusion_system</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>Rigid inclusion foundation system</t>
+          <t>Rigid inclusion system</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>A top-level, complex sampling feature describing the components of a rigid inclusion foundation system - the load transfer platform and the individual rigid inclusion columns constructed within the soil below it.</t>
+          <t>A top-level, complex sampling feature describing the components of a rigid inclusion system - the load transfer platform and the individual rigid inclusion columns constructed within the soil below it.</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>rigid_inclusion</t>
+          <t>ri_column</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>ri_foundation_system</t>
+          <t>rigid_inclusion_system</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
